--- a/MCNP/Target/Station/Rubber/Rubber.xlsx
+++ b/MCNP/Target/Station/Rubber/Rubber.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MyWork\MCNP\Target\Station\Rubber\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1878A8E-9311-4F26-B7F8-8AE856AFCEE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE6B447C-716D-4B84-8D77-3A5E14A5B4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" activeTab="1" xr2:uid="{5E493A83-4E75-40CE-9E48-F182FA9F38C1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{5E493A83-4E75-40CE-9E48-F182FA9F38C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Nuclides" sheetId="1" r:id="rId1"/>
@@ -63920,11 +63920,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="I4" s="4" t="e">
-        <f t="shared" ref="I4:I40" si="5">500*6240000000000*C4*(1-EXP(-H4*10*24*3600))</f>
+        <f t="shared" ref="I4:I39" si="5">500*6240000000000*C4*(1-EXP(-H4*10*24*3600))</f>
         <v>#VALUE!</v>
       </c>
       <c r="J4" s="6" t="e">
-        <f t="shared" ref="J4:J40" si="6">I4*EXP(-H4*10*24*3600)</f>
+        <f t="shared" ref="J4:J36" si="6">I4*EXP(-H4*10*24*3600)</f>
         <v>#VALUE!</v>
       </c>
       <c r="K4" s="7" t="str">
@@ -64062,8 +64062,8 @@
         <v>He6</v>
       </c>
       <c r="U6" s="9">
-        <f>Q6/100</f>
-        <v>6945.6554170076151</v>
+        <f>Q6*0.72/100</f>
+        <v>5000.8719002454827</v>
       </c>
       <c r="V6">
         <f>0</f>
@@ -64239,8 +64239,8 @@
         <v>Li8</v>
       </c>
       <c r="U9" s="9">
-        <f t="shared" ref="U9:U10" si="14">Q9/100</f>
-        <v>16258.013674659696</v>
+        <f t="shared" ref="U9:U10" si="14">Q9*0.72/100</f>
+        <v>11705.769845754981</v>
       </c>
       <c r="V9">
         <f>0</f>
@@ -64315,7 +64315,7 @@
       </c>
       <c r="U10" s="9">
         <f t="shared" si="14"/>
-        <v>38393698.542569511</v>
+        <v>27643462.950650048</v>
       </c>
       <c r="V10">
         <f>0</f>
@@ -64440,8 +64440,8 @@
         <v>Be10</v>
       </c>
       <c r="U12" s="9">
-        <f t="shared" ref="U12:U13" si="21">Q12/100</f>
-        <v>0.27448014874305487</v>
+        <f t="shared" ref="U12:U13" si="21">Q12*0.72/100</f>
+        <v>0.19762570709499949</v>
       </c>
       <c r="V12">
         <f>0</f>
@@ -64516,7 +64516,7 @@
       </c>
       <c r="U13" s="9">
         <f t="shared" si="21"/>
-        <v>33818.691731337596</v>
+        <v>24349.458046563068</v>
       </c>
       <c r="V13">
         <f>0</f>
@@ -64845,8 +64845,8 @@
         <v>C10</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" ref="U19:U20" si="28">Q19/100</f>
-        <v>169957264.09654582</v>
+        <f t="shared" ref="U19:U20" si="28">Q19*0.72/100</f>
+        <v>122369230.14951298</v>
       </c>
       <c r="V19">
         <f>0</f>
@@ -64921,7 +64921,7 @@
       </c>
       <c r="U20" s="9">
         <f t="shared" si="28"/>
-        <v>4585273917.6378489</v>
+        <v>3301397220.6992512</v>
       </c>
       <c r="V20">
         <f>0</f>
@@ -65097,8 +65097,8 @@
         <v>C14</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" ref="U23:U24" si="35">Q23/100</f>
-        <v>636.75941787510465</v>
+        <f t="shared" ref="U23:U24" si="35">Q23*0.72/100</f>
+        <v>458.4667808700753</v>
       </c>
       <c r="V23">
         <f>0</f>
@@ -65173,7 +65173,7 @@
       </c>
       <c r="U24" s="9">
         <f t="shared" si="35"/>
-        <v>291.27412597949746</v>
+        <v>209.71737070523818</v>
       </c>
       <c r="V24">
         <f>0</f>
@@ -65298,8 +65298,8 @@
         <v>N13</v>
       </c>
       <c r="U26" s="9">
-        <f>Q26/100</f>
-        <v>5144176391.8807459</v>
+        <f>Q26*0.72/100</f>
+        <v>3703807002.1541371</v>
       </c>
       <c r="V26">
         <f>0</f>
@@ -65475,8 +65475,8 @@
         <v>N16</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" ref="U29:U30" si="42">Q29/100</f>
-        <v>82613434.320441172</v>
+        <f t="shared" ref="U29:U30" si="42">Q29*0.72/100</f>
+        <v>59481672.710717641</v>
       </c>
       <c r="V29">
         <f>0</f>
@@ -65551,7 +65551,7 @@
       </c>
       <c r="U30" s="9">
         <f t="shared" si="42"/>
-        <v>13619495.818971014</v>
+        <v>9806036.9896591287</v>
       </c>
       <c r="V30">
         <f>0</f>
@@ -65676,8 +65676,8 @@
         <v>O14</v>
       </c>
       <c r="U32" s="9">
-        <f t="shared" ref="U32:U33" si="48">Q32/100</f>
-        <v>2805689017.3711686</v>
+        <f t="shared" ref="U32:U33" si="48">Q32*0.72/100</f>
+        <v>2020096092.5072415</v>
       </c>
       <c r="V32">
         <f>0</f>
@@ -65752,7 +65752,7 @@
       </c>
       <c r="U33" s="9">
         <f t="shared" si="48"/>
-        <v>48205803656.604416</v>
+        <v>34708178632.755173</v>
       </c>
       <c r="V33">
         <f>0</f>
@@ -66132,8 +66132,8 @@
         <v>F18</v>
       </c>
       <c r="U40" s="9">
-        <f>Q40/100</f>
-        <v>43629147.36513786</v>
+        <f>Q40*0.72/100</f>
+        <v>31412986.102899261</v>
       </c>
       <c r="V40">
         <f>0</f>
@@ -68690,7 +68690,7 @@
       </filters>
     </filterColumn>
   </autoFilter>
-  <dataConsolidate leftLabels="1">
+  <dataConsolidate>
     <dataRefs count="1">
       <dataRef ref="B2:C254" sheet="Sheet2"/>
     </dataRefs>
@@ -75522,7 +75522,7 @@
       </filters>
     </filterColumn>
   </autoFilter>
-  <dataConsolidate leftLabels="1">
+  <dataConsolidate>
     <dataRefs count="1">
       <dataRef ref="B1:C1048576" sheet="Sheet3"/>
     </dataRefs>
@@ -81498,7 +81498,7 @@
       </filters>
     </filterColumn>
   </autoFilter>
-  <dataConsolidate leftLabels="1">
+  <dataConsolidate>
     <dataRefs count="1">
       <dataRef ref="B1:C1048576" sheet="Sheet4"/>
     </dataRefs>

--- a/MCNP/Target/Station/Rubber/Rubber.xlsx
+++ b/MCNP/Target/Station/Rubber/Rubber.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MyWork\MCNP\Target\Station\Rubber\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE6B447C-716D-4B84-8D77-3A5E14A5B4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D1C21E-2549-4EA3-A615-844421BDD9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{5E493A83-4E75-40CE-9E48-F182FA9F38C1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{5E493A83-4E75-40CE-9E48-F182FA9F38C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Nuclides" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3434" uniqueCount="3178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3452" uniqueCount="3191">
   <si>
     <t>n</t>
   </si>
@@ -9604,6 +9604,57 @@
   </si>
   <si>
     <t>H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">           </t>
+  </si>
+  <si>
+    <t>EPDM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FFKM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Viton</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PEEK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PTFE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乙丙橡胶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全氟醚橡胶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>氟橡胶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚醚醚酮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚四氟乙烯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸收剂量率Gy/h</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寿命h</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -66251,8 +66302,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C8A9DA8-1955-4552-9A59-5FA845CCBB69}">
   <sheetPr filterMode="1"/>
-  <dimension ref="B2:G254"/>
+  <dimension ref="B2:N254"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="12" max="12" width="14" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2" s="9">
@@ -66458,7 +66512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="B17" s="9">
         <v>3011</v>
       </c>
@@ -66472,7 +66526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="B18" s="9">
         <v>4006</v>
       </c>
@@ -66486,7 +66540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="B19" s="9">
         <v>4007</v>
       </c>
@@ -66500,7 +66554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="B20" s="9">
         <v>4008</v>
       </c>
@@ -66514,7 +66568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="B21" s="9">
         <v>4009</v>
       </c>
@@ -66528,7 +66582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="9">
         <v>4010</v>
       </c>
@@ -66541,8 +66595,11 @@
       <c r="G22" s="9">
         <v>1.9999999999999999E-7</v>
       </c>
-    </row>
-    <row r="23" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="L22" s="9">
+        <v>61.749699999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="B23" s="9">
         <v>4011</v>
       </c>
@@ -66555,8 +66612,11 @@
       <c r="G23" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="L23" t="s">
+        <v>3178</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="B24" s="9">
         <v>4012</v>
       </c>
@@ -66569,8 +66629,11 @@
       <c r="G24" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="L24" s="9">
+        <v>6.9870900000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="B25" s="9">
         <v>4013</v>
       </c>
@@ -66583,8 +66646,11 @@
       <c r="G25" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="L25" t="s">
+        <v>3178</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="B26" s="9">
         <v>4014</v>
       </c>
@@ -66597,8 +66663,11 @@
       <c r="G26" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="L26" s="9">
+        <v>12.6927</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="B27" s="9">
         <v>5008</v>
       </c>
@@ -66611,8 +66680,11 @@
       <c r="G27" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="L27" t="s">
+        <v>3178</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="B28" s="9">
         <v>5009</v>
       </c>
@@ -66625,8 +66697,11 @@
       <c r="G28" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="L28" s="9">
+        <v>133.23099999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="B29" s="9">
         <v>5010</v>
       </c>
@@ -66639,8 +66714,11 @@
       <c r="G29" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="L29" t="s">
+        <v>3178</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="B30" s="9">
         <v>5011</v>
       </c>
@@ -66653,8 +66731,11 @@
       <c r="G30" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="L30" s="9">
+        <v>6.1190499999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="B31" s="9">
         <v>5012</v>
       </c>
@@ -66668,7 +66749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="B32" s="9">
         <v>5013</v>
       </c>
@@ -67130,7 +67211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="B65" s="9">
         <v>8015</v>
       </c>
@@ -67144,7 +67225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B66" s="9">
         <v>1001</v>
       </c>
@@ -67158,7 +67239,7 @@
         <v>1.1000000000000001E-6</v>
       </c>
     </row>
-    <row r="67" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="B67" s="9">
         <v>1002</v>
       </c>
@@ -67172,7 +67253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B68" s="9">
         <v>1003</v>
       </c>
@@ -67186,7 +67267,7 @@
         <v>9.9999999999999995E-8</v>
       </c>
     </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B69" s="9">
         <v>2003</v>
       </c>
@@ -67194,7 +67275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B70" s="9">
         <v>2004</v>
       </c>
@@ -67202,7 +67283,7 @@
         <v>5.9999999999999997E-7</v>
       </c>
     </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B71" s="9">
         <v>2005</v>
       </c>
@@ -67210,7 +67291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B72" s="9">
         <v>2006</v>
       </c>
@@ -67218,79 +67299,165 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B73" s="9">
         <v>2007</v>
       </c>
       <c r="C73" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="J73" s="3"/>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3" t="s">
+        <v>3189</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>3190</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B74" s="9">
         <v>2008</v>
       </c>
       <c r="C74" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="J74" s="3" t="s">
+        <v>3184</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>3179</v>
+      </c>
+      <c r="L74" s="4">
+        <v>61.749699999999997</v>
+      </c>
+      <c r="M74" s="4">
+        <f>500000/L74</f>
+        <v>8097.205330552214</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B75" s="9">
         <v>3005</v>
       </c>
       <c r="C75" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="J75" s="3" t="s">
+        <v>3185</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>3180</v>
+      </c>
+      <c r="L75" s="4">
+        <v>6.9870900000000002</v>
+      </c>
+      <c r="M75" s="4">
+        <f>500000/L75</f>
+        <v>71560.549527771931</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B76" s="9">
         <v>3006</v>
       </c>
       <c r="C76" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="J76" s="3" t="s">
+        <v>3186</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>3181</v>
+      </c>
+      <c r="L76" s="4">
+        <v>12.6927</v>
+      </c>
+      <c r="M76" s="4">
+        <f>400000/L76</f>
+        <v>31514.177440576077</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B77" s="9">
         <v>3007</v>
       </c>
       <c r="C77" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="J77" s="3" t="s">
+        <v>3187</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>3182</v>
+      </c>
+      <c r="L77" s="4">
+        <v>133.23099999999999</v>
+      </c>
+      <c r="M77" s="4">
+        <f>20000000/L77</f>
+        <v>150115.21342630469</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="78" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B78" s="9">
         <v>3008</v>
       </c>
       <c r="C78" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="J78" s="3" t="s">
+        <v>3188</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>3183</v>
+      </c>
+      <c r="L78" s="4">
+        <v>6.1190499999999997</v>
+      </c>
+      <c r="M78" s="4">
+        <f>1000/L78</f>
+        <v>163.42406092448994</v>
+      </c>
+      <c r="N78" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="9">
         <v>3009</v>
       </c>
       <c r="C79" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="L79" t="s">
+        <v>3178</v>
+      </c>
+    </row>
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B80" s="9">
         <v>3010</v>
       </c>
       <c r="C80" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="L80" s="9"/>
+    </row>
+    <row r="81" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B81" s="9">
         <v>3011</v>
       </c>
       <c r="C81" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="L81" t="s">
+        <v>3178</v>
+      </c>
+    </row>
+    <row r="82" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B82" s="9">
         <v>4006</v>
       </c>
@@ -67298,7 +67465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B83" s="9">
         <v>4007</v>
       </c>
@@ -67306,7 +67473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B84" s="9">
         <v>4008</v>
       </c>
@@ -67314,7 +67481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B85" s="9">
         <v>4009</v>
       </c>
@@ -67322,7 +67489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B86" s="9">
         <v>4010</v>
       </c>
@@ -67330,7 +67497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B87" s="9">
         <v>4011</v>
       </c>
@@ -67338,7 +67505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B88" s="9">
         <v>4012</v>
       </c>
@@ -67346,7 +67513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B89" s="9">
         <v>4013</v>
       </c>
@@ -67354,7 +67521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B90" s="9">
         <v>4014</v>
       </c>
@@ -67362,7 +67529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B91" s="9">
         <v>5008</v>
       </c>
@@ -67370,7 +67537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B92" s="9">
         <v>5009</v>
       </c>
@@ -67378,7 +67545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B93" s="9">
         <v>5010</v>
       </c>
@@ -67386,7 +67553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B94" s="9">
         <v>5011</v>
       </c>
@@ -67394,7 +67561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B95" s="9">
         <v>5012</v>
       </c>
@@ -67402,7 +67569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B96" s="9">
         <v>5013</v>
       </c>
